--- a/Jiwei/distri_order2/realization5/Cores.xlsx
+++ b/Jiwei/distri_order2/realization5/Cores.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -515,31 +515,6 @@
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>X4</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>X5</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>X6</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>X7</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>X8</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Zeroes</t>
         </is>
